--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.21.0</t>
+          <t>v0.24.1</t>
         </is>
       </c>
     </row>
@@ -1738,8 +1738,16 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -1748,7 +1756,11 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>1I, 11/13</t>
+        </is>
+      </c>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
@@ -1801,13 +1813,25 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>1I, 11/13</t>
+        </is>
+      </c>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
@@ -1860,8 +1884,16 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
@@ -1870,7 +1902,11 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>1I, 3II/5</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -1923,13 +1959,25 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>1I, 3II/5</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -1978,8 +2026,16 @@
       <c r="K10" s="12" t="inlineStr"/>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -1988,7 +2044,11 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>1I, 3II/5</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
@@ -2037,13 +2097,25 @@
       <c r="K11" s="12" t="inlineStr"/>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>1I, 3II/5</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
@@ -2097,7 +2169,11 @@
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -2106,9 +2182,17 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>1I, 7</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -2160,14 +2244,26 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>1I, 7</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -2219,7 +2315,11 @@
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
@@ -2228,9 +2328,17 @@
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>1I, 7</t>
+        </is>
+      </c>
       <c r="U14" s="12" t="inlineStr"/>
-      <c r="V14" s="11" t="inlineStr"/>
+      <c r="V14" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
@@ -2282,14 +2390,26 @@
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>1I, 7</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
-      <c r="V15" s="11" t="inlineStr"/>
+      <c r="V15" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
@@ -5312,8 +5432,16 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>5, 3II</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -5322,9 +5450,21 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
@@ -5383,15 +5523,35 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>5, 3II</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
-      <c r="V7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
@@ -5451,7 +5611,11 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
@@ -5460,9 +5624,17 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -5522,14 +5694,26 @@
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -5588,8 +5772,16 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>5, 3II</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -5598,9 +5790,21 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -5659,15 +5863,35 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>5, 3II</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -5727,7 +5951,11 @@
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -5736,9 +5964,17 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -5798,14 +6034,26 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -5864,7 +6112,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -5874,7 +6126,11 @@
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -5935,13 +6191,21 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -6002,8 +6266,16 @@
       </c>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
@@ -6012,9 +6284,21 @@
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="12" t="inlineStr"/>
-      <c r="V16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V16" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
@@ -6073,15 +6357,35 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
-      <c r="U17" s="12" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U17" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W17" s="12" t="inlineStr"/>
       <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
@@ -6140,7 +6444,11 @@
       </c>
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -6150,7 +6458,11 @@
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
@@ -6211,13 +6523,21 @@
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -6274,8 +6594,16 @@
       </c>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
-      <c r="O20" s="12" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr">
@@ -6284,9 +6612,21 @@
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
-      <c r="U20" s="12" t="inlineStr"/>
-      <c r="V20" s="11" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U20" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W20" s="12" t="inlineStr"/>
       <c r="X20" s="11" t="inlineStr"/>
       <c r="Y20" s="12" t="inlineStr"/>
@@ -6341,15 +6681,35 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr"/>
       <c r="S21" s="12" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="12" t="inlineStr"/>
-      <c r="V21" s="11" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U21" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="W21" s="12" t="inlineStr"/>
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="12" t="inlineStr"/>
@@ -9199,7 +9559,11 @@
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -9208,8 +9572,16 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 11/13</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -9262,13 +9634,25 @@
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 11/13</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -9325,7 +9709,11 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
@@ -9334,9 +9722,17 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -9392,14 +9788,26 @@
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr"/>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -9455,7 +9863,11 @@
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>3II, 5</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
@@ -9464,8 +9876,16 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 3II/5</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
@@ -9522,13 +9942,25 @@
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>3II, 5</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 3II/5</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
@@ -9585,7 +10017,11 @@
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -9594,9 +10030,17 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr"/>
+      <c r="V12" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -9652,14 +10096,26 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -9715,7 +10171,11 @@
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>3II, 5</t>
+        </is>
+      </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
@@ -9724,8 +10184,16 @@
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="12" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 3II/5</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
@@ -9782,13 +10250,25 @@
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>3II, 5</t>
+        </is>
+      </c>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="12" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 3II/5</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
@@ -9844,7 +10324,11 @@
       </c>
       <c r="L16" s="11" t="inlineStr"/>
       <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -9854,7 +10338,11 @@
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -9911,13 +10399,21 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr"/>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U17" s="12" t="inlineStr"/>
       <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
@@ -9974,8 +10470,16 @@
       </c>
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
@@ -9984,9 +10488,21 @@
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
-      <c r="U18" s="12" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -10041,15 +10557,35 @@
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
-      <c r="U19" s="12" t="inlineStr"/>
-      <c r="V19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W19" s="12" t="inlineStr"/>
       <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
@@ -10104,7 +10640,11 @@
       </c>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -10114,7 +10654,11 @@
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
@@ -10171,13 +10715,21 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O21" s="12" t="inlineStr"/>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr"/>
       <c r="S21" s="12" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
+      <c r="T21" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="U21" s="12" t="inlineStr"/>
       <c r="V21" s="11" t="inlineStr"/>
       <c r="W21" s="12" t="inlineStr"/>
@@ -10230,8 +10782,16 @@
       </c>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="12" t="inlineStr"/>
-      <c r="N22" s="11" t="inlineStr"/>
-      <c r="O22" s="12" t="inlineStr"/>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P22" s="11" t="inlineStr"/>
       <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="11" t="inlineStr">
@@ -10240,9 +10800,21 @@
         </is>
       </c>
       <c r="S22" s="12" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="12" t="inlineStr"/>
-      <c r="V22" s="11" t="inlineStr"/>
+      <c r="T22" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U22" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V22" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W22" s="12" t="inlineStr"/>
       <c r="X22" s="11" t="inlineStr"/>
       <c r="Y22" s="12" t="inlineStr"/>
@@ -10293,15 +10865,35 @@
       </c>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" s="12" t="inlineStr"/>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P23" s="11" t="inlineStr"/>
       <c r="Q23" s="12" t="inlineStr"/>
       <c r="R23" s="11" t="inlineStr"/>
       <c r="S23" s="12" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="12" t="inlineStr"/>
-      <c r="V23" s="11" t="inlineStr"/>
+      <c r="T23" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U23" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+      <c r="V23" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W23" s="12" t="inlineStr"/>
       <c r="X23" s="11" t="inlineStr"/>
       <c r="Y23" s="12" t="inlineStr"/>
@@ -13092,8 +13684,16 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -13102,8 +13702,16 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 1I</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -13163,14 +13771,30 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 1I</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -13226,8 +13850,16 @@
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
@@ -13236,8 +13868,16 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 1I</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -13293,14 +13933,30 @@
       <c r="K9" s="12" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>3II/5, 1I</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
@@ -13360,7 +14016,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -13370,8 +14030,16 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>7, 1I</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
@@ -13431,14 +14099,26 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>7, 1I</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
@@ -13498,7 +14178,11 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -13508,8 +14192,16 @@
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>7, 1I</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
@@ -13569,14 +14261,26 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>7, 1I</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
@@ -16659,7 +17363,11 @@
       </c>
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
@@ -16667,8 +17375,16 @@
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr"/>
-      <c r="X6" s="11" t="inlineStr"/>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="X6" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
       <c r="AA6" s="13" t="inlineStr"/>
@@ -16725,16 +17441,36 @@
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
-      <c r="U7" s="12" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr"/>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
@@ -16792,14 +17528,30 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -16855,16 +17607,36 @@
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
-      <c r="U9" s="12" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="12" t="inlineStr"/>
+      <c r="W9" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
       <c r="Z9" s="11" t="inlineStr"/>
@@ -16918,14 +17690,30 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
@@ -16985,16 +17773,32 @@
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
-      <c r="U11" s="12" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr"/>
+      <c r="W11" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
@@ -17052,14 +17856,26 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
@@ -17115,16 +17931,32 @@
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
-      <c r="U13" s="12" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr"/>
+      <c r="W13" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -17178,14 +18010,26 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
-      <c r="U14" s="12" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
@@ -17245,16 +18089,36 @@
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
-      <c r="U15" s="12" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="12" t="inlineStr"/>
+      <c r="W15" s="12" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
       <c r="Z15" s="11" t="inlineStr"/>
@@ -17312,14 +18176,30 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N16" s="11" t="inlineStr"/>
-      <c r="O16" s="12" t="inlineStr"/>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr"/>
-      <c r="U16" s="12" t="inlineStr"/>
+      <c r="T16" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
@@ -17372,14 +18252,26 @@
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr"/>
       <c r="S17" s="12" t="inlineStr"/>
-      <c r="T17" s="11" t="inlineStr"/>
+      <c r="T17" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U17" s="12" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr"/>
+      <c r="V17" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W17" s="12" t="inlineStr"/>
       <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
@@ -17431,14 +18323,26 @@
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr"/>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr"/>
+      <c r="T18" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U18" s="12" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr"/>
+      <c r="V18" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -17489,13 +18393,21 @@
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr"/>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -17548,13 +18460,21 @@
       </c>
       <c r="L20" s="11" t="inlineStr"/>
       <c r="M20" s="12" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr">
+        <is>
+          <t>3I, 1II</t>
+        </is>
+      </c>
       <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
@@ -17604,7 +18524,11 @@
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="12" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr"/>
@@ -20456,13 +21380,25 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr"/>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
@@ -20515,13 +21451,25 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr"/>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
@@ -20575,14 +21523,26 @@
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr"/>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -20629,13 +21589,25 @@
       <c r="K9" s="12" t="inlineStr"/>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
-      <c r="O9" s="12" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr"/>
+      <c r="T9" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -20689,14 +21661,26 @@
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr"/>
-      <c r="O10" s="12" t="inlineStr"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -20748,14 +21732,26 @@
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr"/>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -20806,13 +21802,21 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
@@ -20862,14 +21866,26 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
-      <c r="T13" s="11" t="inlineStr"/>
+      <c r="T13" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr"/>
+      <c r="V13" s="11" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -20920,13 +21936,21 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr"/>
+      <c r="T14" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -20981,7 +22005,11 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr"/>
+      <c r="T15" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -24600,205 +25628,210 @@
       </c>
       <c r="C17" s="41" t="inlineStr">
         <is>
+          <t xml:space="preserve">OL_delay_dist_weight 0.18
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SWI 1I
+</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1I 24889 24960
+</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OL_delay_dist_bias 15
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE B 3II/5
+</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1II 24960 24889
+</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ARC_delay_dist_weight 0.08
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE C D1
+</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3I 25120 25168
+</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SIG M1
+</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3II 25180 25120
+</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC A1
+</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5 25157 25199
+</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_min_delay 60
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE A 3I
+</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    7 25181 25224
+</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RC_max_delay 255
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE B 1II
+</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    9 25194 25252
+</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_multiple 5
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEC 3I
+</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    11 25217 25274
+</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delay_round_down_allowed False
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NDE A 7
+</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    13 25256 25191
+</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
           <t xml:space="preserve">shunt_sig_filters_fp True
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SWI 1I
-</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1I 24889 24960
-</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_weight 0.18
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">    NDE B 3II/5
 </t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    1II 24960 24889
-</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OL_delay_dist_bias 15
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE C D1
-</t>
-        </is>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    3I 25120 25168
-</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ARC_delay_dist_weight 0.08
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SIG M1
-</t>
-        </is>
-      </c>
-      <c r="B21" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    3II 25180 25120
-</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_circ_multiplier 0.12
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEC A1
-</t>
-        </is>
-      </c>
-      <c r="B22" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    5 25157 25199
-</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ERC_delay_shunt_multiplier 0.36
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE A 3I
-</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    7 25181 25224
-</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_min_delay 60
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE B 1II
-</t>
-        </is>
-      </c>
-      <c r="B24" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    9 25194 25252
-</t>
-        </is>
-      </c>
-      <c r="C24" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RC_max_delay 255
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEC 3I
-</t>
-        </is>
-      </c>
-      <c r="B25" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    11 25217 25274
-</t>
-        </is>
-      </c>
-      <c r="C25" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_multiple 5
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE A 7
-</t>
-        </is>
-      </c>
-      <c r="B26" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    13 25256 25191
-</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delay_round_down_allowed False
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NDE B 3II/5
-</t>
-        </is>
-      </c>
       <c r="B27" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">SIGS
 </t>
         </is>
       </c>
-      <c r="C27" s="41" t="n"/>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vital_fp_threshold 6
+</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
@@ -24813,7 +25846,12 @@
 </t>
         </is>
       </c>
-      <c r="C28" s="41" t="n"/>
+      <c r="C28" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sub_vital_fp_threshold 50
+</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
@@ -24828,7 +25866,12 @@
 </t>
         </is>
       </c>
-      <c r="C29" s="41" t="n"/>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remote_fp_threshold 150
+</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="38" t="inlineStr">

--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.1</t>
+          <t>v0.24.2</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>1I, 11/13</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="U6" s="12" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>1I, 11/13</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="U7" s="12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
       <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr">
         <is>
-          <t>1I, 3II/5</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="U8" s="12" t="inlineStr"/>
@@ -1975,7 +1975,7 @@
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>1I, 3II/5</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="U9" s="12" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr">
         <is>
-          <t>1I, 3II/5</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="U10" s="12" t="inlineStr"/>
@@ -2113,7 +2113,7 @@
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>1I, 3II/5</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr"/>
@@ -2169,11 +2169,7 @@
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -2244,11 +2240,7 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
@@ -2315,11 +2307,7 @@
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
@@ -2390,11 +2378,7 @@
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
@@ -5434,7 +5418,7 @@
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>3II</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -5450,21 +5434,9 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V6" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
@@ -5501,55 +5473,51 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>13+</t>
+          <t>13-</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I</t>
+          <t>5, 3II, 1I</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>11, 1II, 1I</t>
+          <t>11, 13</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>3II, 13</t>
-        </is>
-      </c>
+      <c r="N7" s="11" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>5, 3II</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
-      <c r="R7" s="11" t="inlineStr"/>
+      <c r="R7" s="11" t="inlineStr">
+        <is>
+          <t>11/13, 3II/5, 1I, D1</t>
+        </is>
+      </c>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
+          <t>3I, 1II</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr"/>
+      <c r="V7" s="11" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="V7" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
         </is>
       </c>
       <c r="W7" s="12" t="inlineStr"/>
@@ -5588,53 +5556,45 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>13-</t>
+          <t>13+</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>5, 3II, 1I</t>
+          <t>13, 7, 3I</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 1II, 1I</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5, 3II</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>11/13, 3II/5, 1I, D1</t>
-        </is>
-      </c>
+      <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -5774,7 +5734,7 @@
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>3II</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -5790,21 +5750,9 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -5841,55 +5789,51 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>13+</t>
+          <t>13-</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I</t>
+          <t>11, 5, 3II, 1I</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>1II, 1I</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>3II, 13</t>
-        </is>
-      </c>
+      <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>5, 3II</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
-      <c r="R11" s="11" t="inlineStr"/>
+      <c r="R11" s="11" t="inlineStr">
+        <is>
+          <t>11/13, 3II/5, 1I, D1</t>
+        </is>
+      </c>
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U11" s="12" t="inlineStr">
+          <t>3I, 1II</t>
+        </is>
+      </c>
+      <c r="U11" s="12" t="inlineStr"/>
+      <c r="V11" s="11" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
         </is>
       </c>
       <c r="W11" s="12" t="inlineStr"/>
@@ -5928,53 +5872,45 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>13-</t>
+          <t>13+</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>11, 5, 3II, 1I</t>
+          <t>11, 13, 7, 3I</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1II, 1I</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5, 3II</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
-      <c r="R12" s="11" t="inlineStr">
-        <is>
-          <t>11/13, 3II/5, 1I, D1</t>
-        </is>
-      </c>
+      <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -6169,44 +6105,52 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>3II+</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>9, 3II, 1I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5, 3II, 3I, 1II, 1I</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr"/>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
-      <c r="R15" s="11" t="inlineStr"/>
+      <c r="R15" s="11" t="inlineStr">
+        <is>
+          <t>9, 3II/5, 3I, A1, 1II, 1I, D1</t>
+        </is>
+      </c>
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
-      <c r="U15" s="12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U15" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
@@ -6244,24 +6188,24 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr"/>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9, 3II, 1I</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>5, 3II, 3I, 1II, 1I</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr"/>
@@ -6271,34 +6215,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="O16" s="12" t="inlineStr"/>
       <c r="P16" s="11" t="inlineStr"/>
       <c r="Q16" s="12" t="inlineStr"/>
-      <c r="R16" s="11" t="inlineStr">
-        <is>
-          <t>9, 3II/5, 3I, A1, 1II, 1I, D1</t>
-        </is>
-      </c>
+      <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
       <c r="T16" s="11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
-      <c r="V16" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+          <t>3I, 1II</t>
+        </is>
+      </c>
+      <c r="U16" s="12" t="inlineStr"/>
+      <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
       <c r="Y16" s="12" t="inlineStr"/>
@@ -6357,11 +6285,7 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N17" s="11" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>3II</t>
@@ -6381,11 +6305,7 @@
           <t>11/13</t>
         </is>
       </c>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+      <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
       <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
@@ -6501,44 +6421,48 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>3II+</t>
+          <t>3II-</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>3II, 1I</t>
-        </is>
-      </c>
+      <c r="J19" s="11" t="inlineStr"/>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>9, 5</t>
+          <t>9, 5, 3II, 3I, 1II, 1I</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr"/>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="P19" s="11" t="inlineStr"/>
       <c r="Q19" s="12" t="inlineStr"/>
-      <c r="R19" s="11" t="inlineStr"/>
+      <c r="R19" s="11" t="inlineStr">
+        <is>
+          <t>9, 3II/5, 3I, A1, 1II, 1I, D1</t>
+        </is>
+      </c>
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U19" s="12" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
       <c r="X19" s="11" t="inlineStr"/>
@@ -6576,20 +6500,24 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>3II-</t>
+          <t>3II+</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>3II, 1I</t>
+        </is>
+      </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>9, 5, 3II, 3I, 1II, 1I</t>
+          <t>9, 5</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr"/>
@@ -6599,34 +6527,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr"/>
       <c r="Q20" s="12" t="inlineStr"/>
-      <c r="R20" s="11" t="inlineStr">
-        <is>
-          <t>9, 3II/5, 3I, A1, 1II, 1I, D1</t>
-        </is>
-      </c>
+      <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
       <c r="T20" s="11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U20" s="12" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
-      <c r="V20" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+          <t>3I, 1II</t>
+        </is>
+      </c>
+      <c r="U20" s="12" t="inlineStr"/>
+      <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
       <c r="X20" s="11" t="inlineStr"/>
       <c r="Y20" s="12" t="inlineStr"/>
@@ -6681,11 +6593,7 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N21" s="11" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
           <t>3II</t>
@@ -6705,11 +6613,7 @@
           <t>11/13</t>
         </is>
       </c>
-      <c r="V21" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+      <c r="V21" s="11" t="inlineStr"/>
       <c r="W21" s="12" t="inlineStr"/>
       <c r="X21" s="11" t="inlineStr"/>
       <c r="Y21" s="12" t="inlineStr"/>
@@ -9561,7 +9465,7 @@
       <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr"/>
@@ -9574,7 +9478,7 @@
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 11/13</t>
+          <t>3II/5</t>
         </is>
       </c>
       <c r="U6" s="12" t="inlineStr">
@@ -9636,7 +9540,7 @@
       <c r="N7" s="11" t="inlineStr"/>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr"/>
@@ -9645,7 +9549,7 @@
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 11/13</t>
+          <t>3II/5</t>
         </is>
       </c>
       <c r="U7" s="12" t="inlineStr">
@@ -9765,24 +9669,24 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>1I+</t>
+          <t>1I-</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>1I, 5, 3II</t>
+          <t>3I, 7, 13</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>1I, 1II, 11</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr"/>
@@ -9790,24 +9694,28 @@
       <c r="N9" s="11" t="inlineStr"/>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr"/>
       <c r="Q9" s="12" t="inlineStr"/>
-      <c r="R9" s="11" t="inlineStr"/>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>D1, 1I, 1II, A1, 3I, 7, 11/13</t>
+        </is>
+      </c>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr">
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
+      <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -9840,24 +9748,24 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>1I-</t>
+          <t>1I+</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 13</t>
+          <t>1I, 5, 3II</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>1I, 1II, 11</t>
+          <t>11, 13</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr"/>
@@ -9865,28 +9773,24 @@
       <c r="N10" s="11" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>3II, 5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
-      <c r="R10" s="11" t="inlineStr">
-        <is>
-          <t>D1, 1I, 1II, A1, 3I, 7, 11/13</t>
-        </is>
-      </c>
+      <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 3II/5</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
+          <t>1II, 3I</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr"/>
+      <c r="V10" s="11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -9944,7 +9848,7 @@
       <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>3II, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr"/>
@@ -9953,7 +9857,7 @@
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 3II/5</t>
+          <t>3II/5</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr">
@@ -10073,24 +9977,24 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>1I+</t>
+          <t>1I-</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>1I, 5, 3II, 11</t>
+          <t>3I, 7, 11, 13</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1I, 1II</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr"/>
@@ -10098,24 +10002,28 @@
       <c r="N13" s="11" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
+      <c r="R13" s="11" t="inlineStr">
+        <is>
+          <t>D1, 1I, 1II, A1, 3I, 7, 11/13</t>
+        </is>
+      </c>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
-        </is>
-      </c>
-      <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr">
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U13" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
+      <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -10148,24 +10056,24 @@
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>1I-</t>
+          <t>1I+</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 11, 13</t>
+          <t>1I, 5, 3II, 11</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>1I, 1II</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr"/>
@@ -10173,28 +10081,24 @@
       <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>3II, 5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
-      <c r="R14" s="11" t="inlineStr">
-        <is>
-          <t>D1, 1I, 1II, A1, 3I, 7, 11/13</t>
-        </is>
-      </c>
+      <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 3II/5</t>
-        </is>
-      </c>
-      <c r="U14" s="12" t="inlineStr">
+          <t>1II, 3I</t>
+        </is>
+      </c>
+      <c r="U14" s="12" t="inlineStr"/>
+      <c r="V14" s="11" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
@@ -10252,7 +10156,7 @@
       <c r="N15" s="11" t="inlineStr"/>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>3II, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>
@@ -10261,7 +10165,7 @@
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 3II/5</t>
+          <t>3II/5</t>
         </is>
       </c>
       <c r="U15" s="12" t="inlineStr">
@@ -10377,24 +10281,24 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>1I+</t>
+          <t>1I-</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>1I, 3II, 9</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1I, 1II, 3I, 5, 3II</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr"/>
@@ -10404,14 +10308,22 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O17" s="12" t="inlineStr"/>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P17" s="11" t="inlineStr"/>
       <c r="Q17" s="12" t="inlineStr"/>
-      <c r="R17" s="11" t="inlineStr"/>
+      <c r="R17" s="11" t="inlineStr">
+        <is>
+          <t>D1, 1I, 1II, A1, 3I, 3II/5, 9</t>
+        </is>
+      </c>
       <c r="S17" s="12" t="inlineStr"/>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U17" s="12" t="inlineStr"/>
@@ -10448,24 +10360,24 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>1I-</t>
+          <t>1I+</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1I, 3II, 9</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>1I, 1II, 3I, 5, 3II</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr"/>
@@ -10475,34 +10387,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>3II, 13</t>
-        </is>
-      </c>
+      <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr"/>
       <c r="Q18" s="12" t="inlineStr"/>
-      <c r="R18" s="11" t="inlineStr">
-        <is>
-          <t>D1, 1I, 1II, A1, 3I, 3II/5, 9</t>
-        </is>
-      </c>
+      <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U18" s="12" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
-      <c r="V18" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+          <t>1II, 3I</t>
+        </is>
+      </c>
+      <c r="U18" s="12" t="inlineStr"/>
+      <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -10576,16 +10472,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
-      <c r="V19" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="U19" s="12" t="inlineStr"/>
+      <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
       <c r="X19" s="11" t="inlineStr"/>
       <c r="Y19" s="12" t="inlineStr"/>
@@ -10693,24 +10581,20 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>DOS</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>1I+</t>
+          <t>1I-</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>1I, 3II</t>
-        </is>
-      </c>
+      <c r="J21" s="11" t="inlineStr"/>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>5, 9</t>
+          <t>1I, 1II, 3I, 5, 3II, 9</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr"/>
@@ -10720,14 +10604,22 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O21" s="12" t="inlineStr"/>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>3II, 13</t>
+        </is>
+      </c>
       <c r="P21" s="11" t="inlineStr"/>
       <c r="Q21" s="12" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
+      <c r="R21" s="11" t="inlineStr">
+        <is>
+          <t>D1, 1I, 1II, A1, 3I, 3II/5, 9</t>
+        </is>
+      </c>
       <c r="S21" s="12" t="inlineStr"/>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U21" s="12" t="inlineStr"/>
@@ -10764,20 +10656,24 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>DOS</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>1I-</t>
+          <t>1I+</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr"/>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>1I, 3II</t>
+        </is>
+      </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>1I, 1II, 3I, 5, 3II, 9</t>
+          <t>5, 9</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr"/>
@@ -10787,34 +10683,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>3II, 13</t>
-        </is>
-      </c>
+      <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="11" t="inlineStr"/>
       <c r="Q22" s="12" t="inlineStr"/>
-      <c r="R22" s="11" t="inlineStr">
-        <is>
-          <t>D1, 1I, 1II, A1, 3I, 3II/5, 9</t>
-        </is>
-      </c>
+      <c r="R22" s="11" t="inlineStr"/>
       <c r="S22" s="12" t="inlineStr"/>
       <c r="T22" s="11" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
-      <c r="V22" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+          <t>1II, 3I</t>
+        </is>
+      </c>
+      <c r="U22" s="12" t="inlineStr"/>
+      <c r="V22" s="11" t="inlineStr"/>
       <c r="W22" s="12" t="inlineStr"/>
       <c r="X22" s="11" t="inlineStr"/>
       <c r="Y22" s="12" t="inlineStr"/>
@@ -10884,16 +10764,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="U23" s="12" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="U23" s="12" t="inlineStr"/>
+      <c r="V23" s="11" t="inlineStr"/>
       <c r="W23" s="12" t="inlineStr"/>
       <c r="X23" s="11" t="inlineStr"/>
       <c r="Y23" s="12" t="inlineStr"/>
@@ -13704,14 +13576,10 @@
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 1I</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -13787,14 +13655,10 @@
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 1I</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
@@ -13870,14 +13734,10 @@
       <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 1I</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -13949,14 +13809,10 @@
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 1I</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
@@ -14016,11 +13872,7 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N10" s="11" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -14099,11 +13951,7 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -14178,11 +14026,7 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N12" s="11" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -14261,11 +14105,7 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N13" s="11" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -17455,16 +17295,8 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
+      <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr">
         <is>
@@ -17542,16 +17374,8 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
+      <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -17621,16 +17445,8 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="T9" s="11" t="inlineStr"/>
+      <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr">
         <is>
@@ -17704,16 +17520,8 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr"/>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
+      <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
@@ -17773,11 +17581,7 @@
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -17856,11 +17660,7 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N12" s="11" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -17931,11 +17731,7 @@
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N13" s="11" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -18010,11 +17806,7 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N14" s="11" t="inlineStr"/>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -18103,16 +17895,8 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U15" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="T15" s="11" t="inlineStr"/>
+      <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr">
         <is>
@@ -18190,16 +17974,8 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="T16" s="11" t="inlineStr"/>
+      <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
       <c r="X16" s="11" t="inlineStr"/>
@@ -21394,11 +21170,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
@@ -21465,11 +21237,7 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
@@ -21603,11 +21371,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
+      <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -21732,11 +21496,7 @@
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
@@ -21866,11 +21626,7 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>

--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v0.24.2</t>
+          <t>v1.0.0</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1I, 3II</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1756,11 +1756,7 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
@@ -1815,7 +1811,7 @@
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1I, 3II</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr">
@@ -1827,11 +1823,7 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
@@ -1886,7 +1878,7 @@
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1I, 3II</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -1902,11 +1894,7 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -1961,7 +1949,7 @@
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1I, 3II</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr">
@@ -1973,11 +1961,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -2028,7 +2012,7 @@
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1I, 3II</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -2044,11 +2028,7 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T10" s="11" t="inlineStr"/>
       <c r="U10" s="12" t="inlineStr"/>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
@@ -2099,7 +2079,7 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>1I, 3II</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr">
@@ -2111,11 +2091,7 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
-      <c r="T11" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T11" s="11" t="inlineStr"/>
       <c r="U11" s="12" t="inlineStr"/>
       <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
@@ -2168,8 +2144,16 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
@@ -2180,15 +2164,11 @@
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr">
         <is>
-          <t>1I, 7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -2239,23 +2219,27 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>1I, 7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -2306,8 +2290,16 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
@@ -2318,15 +2310,11 @@
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr">
         <is>
-          <t>1I, 7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U14" s="12" t="inlineStr"/>
-      <c r="V14" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
@@ -2377,23 +2365,27 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>1I, 7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U15" s="12" t="inlineStr"/>
-      <c r="V15" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
@@ -5416,14 +5408,10 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>5, 3II</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr"/>
@@ -5434,8 +5422,16 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr"/>
-      <c r="U6" s="12" t="inlineStr"/>
+      <c r="T6" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
       <c r="X6" s="11" t="inlineStr"/>
@@ -5495,7 +5491,11 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -5511,15 +5511,11 @@
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
+          <t>9, 3I</t>
         </is>
       </c>
       <c r="U7" s="12" t="inlineStr"/>
-      <c r="V7" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
@@ -5578,22 +5574,26 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="N8" s="11" t="inlineStr"/>
       <c r="O8" s="12" t="inlineStr">
         <is>
-          <t>5, 3II</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr"/>
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr"/>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr"/>
-      <c r="U8" s="12" t="inlineStr"/>
+      <c r="T8" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U8" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
@@ -5653,7 +5653,11 @@
       </c>
       <c r="L9" s="11" t="inlineStr"/>
       <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="11" t="inlineStr"/>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -5665,15 +5669,11 @@
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
+          <t>9, 3I</t>
         </is>
       </c>
       <c r="U9" s="12" t="inlineStr"/>
-      <c r="V9" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
@@ -5732,14 +5732,10 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="N10" s="11" t="inlineStr"/>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>5, 3II</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr"/>
@@ -5750,8 +5746,16 @@
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
-      <c r="T10" s="11" t="inlineStr"/>
-      <c r="U10" s="12" t="inlineStr"/>
+      <c r="T10" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
@@ -5811,7 +5815,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -5827,15 +5835,11 @@
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
+          <t>9, 3I</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -5894,22 +5898,26 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>3II</t>
-        </is>
-      </c>
+      <c r="N12" s="11" t="inlineStr"/>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>5, 3II</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr"/>
-      <c r="U12" s="12" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr">
+        <is>
+          <t>3II/5</t>
+        </is>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
@@ -5969,7 +5977,11 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -5981,15 +5993,11 @@
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
+          <t>9, 3I</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -6050,7 +6058,7 @@
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I, 1II</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
@@ -6062,11 +6070,7 @@
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -6127,7 +6131,11 @@
       </c>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
           <t>3II</t>
@@ -6212,7 +6220,7 @@
       <c r="M16" s="12" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I, 1II</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
@@ -6220,11 +6228,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr"/>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -6285,7 +6289,11 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>3II</t>
@@ -6366,7 +6374,7 @@
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I, 1II</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
@@ -6378,11 +6386,7 @@
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
@@ -6439,7 +6443,11 @@
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
           <t>3II</t>
@@ -6524,7 +6532,7 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I, 1II</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -6532,11 +6540,7 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
@@ -6593,7 +6597,11 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
           <t>3II</t>
@@ -9462,12 +9470,12 @@
       </c>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="12" t="inlineStr"/>
-      <c r="N6" s="11" t="inlineStr"/>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
+      <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr"/>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
@@ -9478,7 +9486,7 @@
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>3II/5</t>
+          <t>3II/5, 11/13</t>
         </is>
       </c>
       <c r="U6" s="12" t="inlineStr">
@@ -9537,19 +9545,19 @@
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
-      <c r="N7" s="11" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
+      <c r="O7" s="12" t="inlineStr"/>
       <c r="P7" s="11" t="inlineStr"/>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>3II/5</t>
+          <t>3II/5, 11/13</t>
         </is>
       </c>
       <c r="U7" s="12" t="inlineStr">
@@ -9612,7 +9620,11 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -9628,15 +9640,11 @@
       <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -9770,7 +9778,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -9782,15 +9794,11 @@
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -9920,7 +9928,11 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -9936,15 +9948,11 @@
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U12" s="12" t="inlineStr"/>
-      <c r="V12" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
       <c r="X12" s="11" t="inlineStr"/>
       <c r="Y12" s="12" t="inlineStr"/>
@@ -10078,7 +10086,11 @@
       </c>
       <c r="L14" s="11" t="inlineStr"/>
       <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>1II, 3I</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -10090,15 +10102,11 @@
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U14" s="12" t="inlineStr"/>
-      <c r="V14" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
       <c r="X14" s="11" t="inlineStr"/>
       <c r="Y14" s="12" t="inlineStr"/>
@@ -10230,7 +10238,7 @@
       <c r="M16" s="12" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1II, 13, 3I</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
@@ -10242,11 +10250,7 @@
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
-      <c r="T16" s="11" t="inlineStr">
-        <is>
-          <t>1II, 3I</t>
-        </is>
-      </c>
+      <c r="T16" s="11" t="inlineStr"/>
       <c r="U16" s="12" t="inlineStr"/>
       <c r="V16" s="11" t="inlineStr"/>
       <c r="W16" s="12" t="inlineStr"/>
@@ -10303,14 +10307,10 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N17" s="11" t="inlineStr"/>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>3II</t>
         </is>
       </c>
       <c r="P17" s="11" t="inlineStr"/>
@@ -10323,7 +10323,7 @@
       <c r="S17" s="12" t="inlineStr"/>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U17" s="12" t="inlineStr"/>
@@ -10384,7 +10384,7 @@
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1II, 13, 3I</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
@@ -10392,11 +10392,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr"/>
       <c r="S18" s="12" t="inlineStr"/>
-      <c r="T18" s="11" t="inlineStr">
-        <is>
-          <t>1II, 3I</t>
-        </is>
-      </c>
+      <c r="T18" s="11" t="inlineStr"/>
       <c r="U18" s="12" t="inlineStr"/>
       <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
@@ -10453,14 +10449,10 @@
       </c>
       <c r="L19" s="11" t="inlineStr"/>
       <c r="M19" s="12" t="inlineStr"/>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N19" s="11" t="inlineStr"/>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>3II</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr"/>
@@ -10469,7 +10461,7 @@
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U19" s="12" t="inlineStr"/>
@@ -10530,7 +10522,7 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1II, 13, 3I</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -10542,11 +10534,7 @@
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>1II, 3I</t>
-        </is>
-      </c>
+      <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
@@ -10599,14 +10587,10 @@
       </c>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="12" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N21" s="11" t="inlineStr"/>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>3II</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr"/>
@@ -10619,7 +10603,7 @@
       <c r="S21" s="12" t="inlineStr"/>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U21" s="12" t="inlineStr"/>
@@ -10680,7 +10664,7 @@
       <c r="M22" s="12" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1II, 13, 3I</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr"/>
@@ -10688,11 +10672,7 @@
       <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="11" t="inlineStr"/>
       <c r="S22" s="12" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr">
-        <is>
-          <t>1II, 3I</t>
-        </is>
-      </c>
+      <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="12" t="inlineStr"/>
       <c r="V22" s="11" t="inlineStr"/>
       <c r="W22" s="12" t="inlineStr"/>
@@ -10745,14 +10725,10 @@
       </c>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="12" t="inlineStr"/>
-      <c r="N23" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="N23" s="11" t="inlineStr"/>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>3II, 13</t>
+          <t>3II</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr"/>
@@ -10761,7 +10737,7 @@
       <c r="S23" s="12" t="inlineStr"/>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U23" s="12" t="inlineStr"/>
@@ -13558,7 +13534,7 @@
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>3II, 1I</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -13574,11 +13550,7 @@
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
-      <c r="T6" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
       <c r="W6" s="12" t="inlineStr"/>
@@ -13641,7 +13613,7 @@
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>3II, 1I</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr">
@@ -13653,11 +13625,7 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
-      <c r="T7" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
       <c r="W7" s="12" t="inlineStr"/>
@@ -13716,7 +13684,7 @@
       <c r="M8" s="12" t="inlineStr"/>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>3II, 1I</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -13732,11 +13700,7 @@
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
-      <c r="T8" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T8" s="11" t="inlineStr"/>
       <c r="U8" s="12" t="inlineStr"/>
       <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
@@ -13795,7 +13759,7 @@
       <c r="M9" s="12" t="inlineStr"/>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>3II</t>
+          <t>3II, 1I</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr">
@@ -13807,11 +13771,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
-      <c r="T9" s="11" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
       <c r="W9" s="12" t="inlineStr"/>
@@ -13872,7 +13832,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>13, 1I</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr"/>
       <c r="P10" s="11" t="inlineStr"/>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -13884,7 +13848,7 @@
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr">
         <is>
-          <t>7, 1I</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U10" s="12" t="inlineStr">
@@ -13951,7 +13915,11 @@
       </c>
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>13, 1I</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -13959,7 +13927,7 @@
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>7, 1I</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr">
@@ -14026,7 +13994,11 @@
       </c>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>13, 1I</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -14038,7 +14010,7 @@
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr">
         <is>
-          <t>7, 1I</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U12" s="12" t="inlineStr">
@@ -14105,7 +14077,11 @@
       </c>
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>13, 1I</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -14113,7 +14089,7 @@
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>7, 1I</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr">
@@ -17208,23 +17184,19 @@
           <t>3II</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr"/>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>3II</t>
+        </is>
+      </c>
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr"/>
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr"/>
       <c r="U6" s="12" t="inlineStr"/>
       <c r="V6" s="11" t="inlineStr"/>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>3II/5</t>
-        </is>
-      </c>
-      <c r="X6" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="W6" s="12" t="inlineStr"/>
+      <c r="X6" s="11" t="inlineStr"/>
       <c r="Y6" s="12" t="inlineStr"/>
       <c r="Z6" s="11" t="inlineStr"/>
       <c r="AA6" s="13" t="inlineStr"/>
@@ -17291,18 +17263,18 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr"/>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr"/>
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr"/>
       <c r="U7" s="12" t="inlineStr"/>
       <c r="V7" s="11" t="inlineStr"/>
-      <c r="W7" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="W7" s="12" t="inlineStr"/>
       <c r="X7" s="11" t="inlineStr"/>
       <c r="Y7" s="12" t="inlineStr"/>
       <c r="Z7" s="11" t="inlineStr"/>
@@ -17441,18 +17413,18 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr"/>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr"/>
       <c r="S9" s="12" t="inlineStr"/>
       <c r="T9" s="11" t="inlineStr"/>
       <c r="U9" s="12" t="inlineStr"/>
       <c r="V9" s="11" t="inlineStr"/>
-      <c r="W9" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="W9" s="12" t="inlineStr"/>
       <c r="X9" s="11" t="inlineStr"/>
       <c r="Y9" s="12" t="inlineStr"/>
       <c r="Z9" s="11" t="inlineStr"/>
@@ -17581,9 +17553,17 @@
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
+      <c r="P11" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
@@ -17598,11 +17578,7 @@
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
-      <c r="W11" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
       <c r="Z11" s="11" t="inlineStr"/>
@@ -17660,7 +17636,11 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O12" s="12" t="inlineStr"/>
       <c r="P12" s="11" t="inlineStr"/>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -17731,9 +17711,17 @@
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O13" s="12" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
+      <c r="P13" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
@@ -17748,11 +17736,7 @@
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
-      <c r="W13" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
       <c r="Z13" s="11" t="inlineStr"/>
@@ -17806,7 +17790,11 @@
           <t>1II</t>
         </is>
       </c>
-      <c r="N14" s="11" t="inlineStr"/>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="O14" s="12" t="inlineStr"/>
       <c r="P14" s="11" t="inlineStr"/>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -17891,18 +17879,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>1I</t>
+        </is>
+      </c>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr"/>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
-      <c r="W15" s="12" t="inlineStr">
-        <is>
-          <t>1I</t>
-        </is>
-      </c>
+      <c r="W15" s="12" t="inlineStr"/>
       <c r="X15" s="11" t="inlineStr"/>
       <c r="Y15" s="12" t="inlineStr"/>
       <c r="Z15" s="11" t="inlineStr"/>
@@ -18027,7 +18015,11 @@
       </c>
       <c r="L17" s="11" t="inlineStr"/>
       <c r="M17" s="12" t="inlineStr"/>
-      <c r="N17" s="11" t="inlineStr"/>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -18039,15 +18031,11 @@
       <c r="S17" s="12" t="inlineStr"/>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
+          <t>9, 3I</t>
         </is>
       </c>
       <c r="U17" s="12" t="inlineStr"/>
-      <c r="V17" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V17" s="11" t="inlineStr"/>
       <c r="W17" s="12" t="inlineStr"/>
       <c r="X17" s="11" t="inlineStr"/>
       <c r="Y17" s="12" t="inlineStr"/>
@@ -18098,7 +18086,11 @@
       </c>
       <c r="L18" s="11" t="inlineStr"/>
       <c r="M18" s="12" t="inlineStr"/>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -18110,15 +18102,11 @@
       <c r="S18" s="12" t="inlineStr"/>
       <c r="T18" s="11" t="inlineStr">
         <is>
-          <t>3I, 1II</t>
+          <t>9, 3I</t>
         </is>
       </c>
       <c r="U18" s="12" t="inlineStr"/>
-      <c r="V18" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V18" s="11" t="inlineStr"/>
       <c r="W18" s="12" t="inlineStr"/>
       <c r="X18" s="11" t="inlineStr"/>
       <c r="Y18" s="12" t="inlineStr"/>
@@ -18171,7 +18159,7 @@
       <c r="M19" s="12" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I, 1II</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr"/>
@@ -18179,11 +18167,7 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr"/>
       <c r="S19" s="12" t="inlineStr"/>
-      <c r="T19" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T19" s="11" t="inlineStr"/>
       <c r="U19" s="12" t="inlineStr"/>
       <c r="V19" s="11" t="inlineStr"/>
       <c r="W19" s="12" t="inlineStr"/>
@@ -18238,7 +18222,7 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I, 1II</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -18246,11 +18230,7 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr"/>
       <c r="S20" s="12" t="inlineStr"/>
-      <c r="T20" s="11" t="inlineStr">
-        <is>
-          <t>3I, 1II</t>
-        </is>
-      </c>
+      <c r="T20" s="11" t="inlineStr"/>
       <c r="U20" s="12" t="inlineStr"/>
       <c r="V20" s="11" t="inlineStr"/>
       <c r="W20" s="12" t="inlineStr"/>
@@ -21290,7 +21270,11 @@
       </c>
       <c r="L8" s="11" t="inlineStr"/>
       <c r="M8" s="12" t="inlineStr"/>
-      <c r="N8" s="11" t="inlineStr"/>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O8" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -21302,15 +21286,11 @@
       <c r="S8" s="12" t="inlineStr"/>
       <c r="T8" s="11" t="inlineStr">
         <is>
-          <t>3I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U8" s="12" t="inlineStr"/>
-      <c r="V8" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V8" s="11" t="inlineStr"/>
       <c r="W8" s="12" t="inlineStr"/>
       <c r="X8" s="11" t="inlineStr"/>
       <c r="Y8" s="12" t="inlineStr"/>
@@ -21424,7 +21404,11 @@
       </c>
       <c r="L10" s="11" t="inlineStr"/>
       <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="11" t="inlineStr"/>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>3I</t>
+        </is>
+      </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
           <t>7</t>
@@ -21436,15 +21420,11 @@
       <c r="S10" s="12" t="inlineStr"/>
       <c r="T10" s="11" t="inlineStr">
         <is>
-          <t>3I</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U10" s="12" t="inlineStr"/>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="V10" s="11" t="inlineStr"/>
       <c r="W10" s="12" t="inlineStr"/>
       <c r="X10" s="11" t="inlineStr"/>
       <c r="Y10" s="12" t="inlineStr"/>
@@ -21496,22 +21476,22 @@
       <c r="L11" s="11" t="inlineStr"/>
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr"/>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P11" s="11" t="inlineStr"/>
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr"/>
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr"/>
-      <c r="V11" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="V11" s="11" t="inlineStr"/>
       <c r="W11" s="12" t="inlineStr"/>
       <c r="X11" s="11" t="inlineStr"/>
       <c r="Y11" s="12" t="inlineStr"/>
@@ -21564,7 +21544,7 @@
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr"/>
@@ -21572,11 +21552,7 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr"/>
       <c r="S12" s="12" t="inlineStr"/>
-      <c r="T12" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="T12" s="11" t="inlineStr"/>
       <c r="U12" s="12" t="inlineStr"/>
       <c r="V12" s="11" t="inlineStr"/>
       <c r="W12" s="12" t="inlineStr"/>
@@ -21626,22 +21602,22 @@
       <c r="L13" s="11" t="inlineStr"/>
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr"/>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P13" s="11" t="inlineStr"/>
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr"/>
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7, 11/13</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr"/>
-      <c r="V13" s="11" t="inlineStr">
-        <is>
-          <t>11/13</t>
-        </is>
-      </c>
+      <c r="V13" s="11" t="inlineStr"/>
       <c r="W13" s="12" t="inlineStr"/>
       <c r="X13" s="11" t="inlineStr"/>
       <c r="Y13" s="12" t="inlineStr"/>
@@ -21694,7 +21670,7 @@
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13, 3I</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
@@ -21702,11 +21678,7 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr"/>
       <c r="S14" s="12" t="inlineStr"/>
-      <c r="T14" s="11" t="inlineStr">
-        <is>
-          <t>3I</t>
-        </is>
-      </c>
+      <c r="T14" s="11" t="inlineStr"/>
       <c r="U14" s="12" t="inlineStr"/>
       <c r="V14" s="11" t="inlineStr"/>
       <c r="W14" s="12" t="inlineStr"/>
@@ -21755,17 +21727,17 @@
       <c r="K15" s="12" t="inlineStr"/>
       <c r="L15" s="11" t="inlineStr"/>
       <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="11" t="inlineStr"/>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>1II</t>
+        </is>
+      </c>
       <c r="O15" s="12" t="inlineStr"/>
       <c r="P15" s="11" t="inlineStr"/>
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr"/>
       <c r="S15" s="12" t="inlineStr"/>
-      <c r="T15" s="11" t="inlineStr">
-        <is>
-          <t>1II</t>
-        </is>
-      </c>
+      <c r="T15" s="11" t="inlineStr"/>
       <c r="U15" s="12" t="inlineStr"/>
       <c r="V15" s="11" t="inlineStr"/>
       <c r="W15" s="12" t="inlineStr"/>
@@ -25195,7 +25167,7 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_ol_distance 120
+          <t xml:space="preserve">main_ol_distance 150
 </t>
         </is>
       </c>

--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -25167,7 +25167,7 @@
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">main_ol_distance 150
+          <t xml:space="preserve">main_ol_distance 120
 </t>
         </is>
       </c>

--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -1206,7 +1206,7 @@
       <c r="E3" s="49" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.0</t>
+          <t>v1.0.1</t>
         </is>
       </c>
     </row>

--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -24992,7 +24992,7 @@
       </c>
       <c r="C1" s="36" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Operational Parameters</t>
         </is>
       </c>
       <c r="D1" s="37" t="inlineStr">

--- a/stations/output/CIS_Interlocking_Program.xlsx
+++ b/stations/output/CIS_Interlocking_Program.xlsx
@@ -462,15 +462,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -479,37 +470,6 @@
         <color theme="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -531,30 +491,6 @@
       <top style="thin">
         <color theme="1"/>
       </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
@@ -585,6 +521,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="1"/>
@@ -592,6 +561,15 @@
       <top style="medium">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -609,6 +587,17 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color theme="1"/>
@@ -639,12 +628,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -788,9 +788,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -818,29 +815,42 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1183,49 +1193,49 @@
       <c r="B1" s="21" t="n"/>
       <c r="C1" s="21" t="n"/>
       <c r="D1" s="21" t="n"/>
-      <c r="E1" s="59" t="inlineStr">
+      <c r="E1" s="61" t="inlineStr">
         <is>
           <t>ZIRCON</t>
         </is>
       </c>
-      <c r="F1" s="60" t="n"/>
+      <c r="F1" s="62" t="n"/>
     </row>
     <row r="2" ht="16.2" customHeight="1" thickBot="1">
-      <c r="A2" s="22" t="n"/>
-      <c r="B2" s="49" t="n"/>
-      <c r="C2" s="49" t="n"/>
-      <c r="D2" s="49" t="n"/>
-      <c r="E2" s="61" t="n"/>
-      <c r="F2" s="62" t="n"/>
+      <c r="A2" s="58" t="n"/>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="64" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="49" t="n"/>
-      <c r="C3" s="49" t="n"/>
-      <c r="D3" s="49" t="n"/>
-      <c r="E3" s="49" t="n"/>
+      <c r="A3" s="58" t="n"/>
+      <c r="B3" s="59" t="n"/>
+      <c r="C3" s="59" t="n"/>
+      <c r="D3" s="59" t="n"/>
+      <c r="E3" s="59" t="n"/>
       <c r="F3" s="29" t="inlineStr">
         <is>
-          <t>v1.0.1</t>
+          <t>v1.0.2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="n"/>
-      <c r="B4" s="49" t="n"/>
-      <c r="C4" s="49" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="23" t="n"/>
+      <c r="A4" s="58" t="n"/>
+      <c r="B4" s="59" t="n"/>
+      <c r="C4" s="59" t="n"/>
+      <c r="D4" s="59" t="n"/>
+      <c r="E4" s="59" t="n"/>
+      <c r="F4" s="60" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="n"/>
+      <c r="A5" s="58" t="n"/>
       <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Interlocking Program</t>
         </is>
       </c>
-      <c r="F5" s="23" t="n"/>
+      <c r="F5" s="60" t="n"/>
     </row>
     <row r="6" ht="14.4" customHeight="1">
       <c r="A6" s="24" t="n"/>
@@ -1240,94 +1250,92 @@
       <c r="F7" s="25" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n"/>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>Cascais (CIS)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="n"/>
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>Cascais (NOT REAL DATA - FOR TESTING ONLY) (CIS)</t>
+        </is>
+      </c>
+      <c r="F8" s="66" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="A9" s="65" t="inlineStr">
         <is>
           <t>Linha de Cascais</t>
         </is>
       </c>
-      <c r="F9" s="23" t="n"/>
+      <c r="F9" s="66" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="23" t="n"/>
+      <c r="A10" s="58" t="n"/>
+      <c r="B10" s="59" t="n"/>
+      <c r="C10" s="59" t="n"/>
+      <c r="D10" s="59" t="n"/>
+      <c r="E10" s="59" t="n"/>
+      <c r="F10" s="60" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n"/>
-      <c r="B11" s="49" t="n"/>
-      <c r="C11" s="49" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="23" t="n"/>
+      <c r="A11" s="58" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="60" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="n"/>
-      <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="23" t="n"/>
+      <c r="A12" s="58" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="60" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n"/>
-      <c r="B13" s="49" t="n"/>
-      <c r="C13" s="49" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="23" t="n"/>
+      <c r="A13" s="58" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="60" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="23" t="n"/>
+      <c r="A14" s="58" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="60" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n"/>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="23" t="n"/>
+      <c r="A15" s="58" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="60" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="23" t="n"/>
+      <c r="A16" s="58" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="60" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n"/>
-      <c r="B17" s="49" t="n"/>
-      <c r="C17" s="49" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="23" t="n"/>
+      <c r="A17" s="58" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="60" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="23" t="n"/>
+      <c r="A18" s="58" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="60" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
@@ -1335,11 +1343,11 @@
           <t>Diogo Luís</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n"/>
-      <c r="C19" s="49" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="23" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="n"/>
     </row>
     <row r="20" ht="16.2" customHeight="1" thickBot="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1355,9 +1363,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B5:E6"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="E1:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1385,310 +1393,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -1745,7 +1753,7 @@
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr"/>
@@ -1816,7 +1824,7 @@
       </c>
       <c r="O7" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr"/>
@@ -1866,7 +1874,7 @@
       <c r="I8" s="10" t="inlineStr"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I, 7, 13</t>
+          <t>1II, 3I, 7, 15</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -1890,7 +1898,7 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>1II, A1, 3I, 7, 11/13</t>
+          <t>1II, A1, 3I, 7, 11/15</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
@@ -1937,7 +1945,7 @@
       <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I, 7, 13</t>
+          <t>1II, 3I, 7, 15</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -2004,7 +2012,7 @@
       <c r="I10" s="10" t="inlineStr"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I, 7, 11, 13</t>
+          <t>1II, 3I, 7, 11, 15</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr"/>
@@ -2024,7 +2032,7 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>1II, A1, 3I, 7, 11/13</t>
+          <t>1II, A1, 3I, 7, 11/15</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
@@ -2071,7 +2079,7 @@
       <c r="I11" s="10" t="inlineStr"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>1II, 3I, 7, 11, 13</t>
+          <t>1II, 3I, 7, 11, 15</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr"/>
@@ -2151,7 +2159,7 @@
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr"/>
@@ -2164,7 +2172,7 @@
       <c r="S12" s="12" t="inlineStr"/>
       <c r="T12" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U12" s="12" t="inlineStr"/>
@@ -2226,7 +2234,7 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr"/>
@@ -2235,7 +2243,7 @@
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr"/>
@@ -2297,7 +2305,7 @@
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr"/>
@@ -2310,7 +2318,7 @@
       <c r="S14" s="12" t="inlineStr"/>
       <c r="T14" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U14" s="12" t="inlineStr"/>
@@ -2372,7 +2380,7 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr"/>
@@ -2381,7 +2389,7 @@
       <c r="S15" s="12" t="inlineStr"/>
       <c r="T15" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U15" s="12" t="inlineStr"/>
@@ -5051,310 +5059,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -5366,7 +5374,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -5392,13 +5400,13 @@
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>13+</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I</t>
+          <t>15, 7, 3I</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -5418,7 +5426,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>11/13, 7, 3I, A1, 1II, 1I, D1</t>
+          <t>11/15, 7, 3I, A1, 1II, 1I, B1</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
@@ -5449,7 +5457,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -5475,7 +5483,7 @@
       <c r="G7" s="10" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>13-</t>
+          <t>15-</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr"/>
@@ -5486,7 +5494,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 15</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
@@ -5505,7 +5513,7 @@
       <c r="Q7" s="12" t="inlineStr"/>
       <c r="R7" s="11" t="inlineStr">
         <is>
-          <t>11/13, 3II/5, 1I, D1</t>
+          <t>11/15, 3II/5, 1I, B1</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr"/>
@@ -5532,7 +5540,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -5558,13 +5566,13 @@
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>13+</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I</t>
+          <t>15, 7, 3I</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -5611,7 +5619,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -5637,7 +5645,7 @@
       <c r="G9" s="10" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>13-</t>
+          <t>15-</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr"/>
@@ -5648,7 +5656,7 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 15</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr"/>
@@ -5716,13 +5724,13 @@
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>13+</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I</t>
+          <t>11, 15, 7, 3I</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -5742,7 +5750,7 @@
       <c r="Q10" s="12" t="inlineStr"/>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>11/13, 7, 3I, A1, 1II, 1I, D1</t>
+          <t>11/15, 7, 3I, A1, 1II, 1I, B1</t>
         </is>
       </c>
       <c r="S10" s="12" t="inlineStr"/>
@@ -5799,7 +5807,7 @@
       <c r="G11" s="10" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>13-</t>
+          <t>15-</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr"/>
@@ -5810,7 +5818,7 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr"/>
@@ -5829,7 +5837,7 @@
       <c r="Q11" s="12" t="inlineStr"/>
       <c r="R11" s="11" t="inlineStr">
         <is>
-          <t>11/13, 3II/5, 1I, D1</t>
+          <t>11/15, 3II/5, 1I, B1</t>
         </is>
       </c>
       <c r="S11" s="12" t="inlineStr"/>
@@ -5882,13 +5890,13 @@
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>13+</t>
+          <t>15+</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I</t>
+          <t>11, 15, 7, 3I</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -5961,7 +5969,7 @@
       <c r="G13" s="10" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>13-</t>
+          <t>15-</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr"/>
@@ -5972,7 +5980,7 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr"/>
@@ -6058,7 +6066,7 @@
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>13, 3I, 1II</t>
+          <t>15, 3I, 1II</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
@@ -6066,7 +6074,7 @@
       <c r="Q14" s="12" t="inlineStr"/>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>9, 3II/5, 1I, D1</t>
+          <t>9, 3II/5, 1I, B1</t>
         </is>
       </c>
       <c r="S14" s="12" t="inlineStr"/>
@@ -6133,7 +6141,7 @@
       <c r="M15" s="12" t="inlineStr"/>
       <c r="N15" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
@@ -6145,7 +6153,7 @@
       <c r="Q15" s="12" t="inlineStr"/>
       <c r="R15" s="11" t="inlineStr">
         <is>
-          <t>9, 3II/5, 3I, A1, 1II, 1I, D1</t>
+          <t>9, 3II/5, 3I, A1, 1II, 1I, B1</t>
         </is>
       </c>
       <c r="S15" s="12" t="inlineStr"/>
@@ -6156,7 +6164,7 @@
       </c>
       <c r="U15" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V15" s="11" t="inlineStr"/>
@@ -6220,7 +6228,7 @@
       <c r="M16" s="12" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>13, 3I, 1II</t>
+          <t>15, 3I, 1II</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
@@ -6291,7 +6299,7 @@
       <c r="M17" s="12" t="inlineStr"/>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr">
@@ -6310,7 +6318,7 @@
       </c>
       <c r="U17" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V17" s="11" t="inlineStr"/>
@@ -6374,7 +6382,7 @@
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>13, 3I, 1II</t>
+          <t>15, 3I, 1II</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
@@ -6382,7 +6390,7 @@
       <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>9, 3II/5, 1I, D1</t>
+          <t>9, 3II/5, 1I, B1</t>
         </is>
       </c>
       <c r="S18" s="12" t="inlineStr"/>
@@ -6445,7 +6453,7 @@
       <c r="M19" s="12" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr">
@@ -6457,7 +6465,7 @@
       <c r="Q19" s="12" t="inlineStr"/>
       <c r="R19" s="11" t="inlineStr">
         <is>
-          <t>9, 3II/5, 3I, A1, 1II, 1I, D1</t>
+          <t>9, 3II/5, 3I, A1, 1II, 1I, B1</t>
         </is>
       </c>
       <c r="S19" s="12" t="inlineStr"/>
@@ -6468,7 +6476,7 @@
       </c>
       <c r="U19" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V19" s="11" t="inlineStr"/>
@@ -6532,7 +6540,7 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>13, 3I, 1II</t>
+          <t>15, 3I, 1II</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -6599,7 +6607,7 @@
       <c r="M21" s="12" t="inlineStr"/>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O21" s="12" t="inlineStr">
@@ -6618,7 +6626,7 @@
       </c>
       <c r="U21" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V21" s="11" t="inlineStr"/>
@@ -9117,310 +9125,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -9472,7 +9480,7 @@
       <c r="M6" s="12" t="inlineStr"/>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr"/>
@@ -9480,13 +9488,13 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 1II, A1, 3I, 7</t>
+          <t>B1, 1I, 1II, A1, 3I, 7</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
       <c r="T6" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 11/13</t>
+          <t>3II/5, 11/15</t>
         </is>
       </c>
       <c r="U6" s="12" t="inlineStr">
@@ -9547,7 +9555,7 @@
       <c r="M7" s="12" t="inlineStr"/>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O7" s="12" t="inlineStr"/>
@@ -9557,7 +9565,7 @@
       <c r="S7" s="12" t="inlineStr"/>
       <c r="T7" s="11" t="inlineStr">
         <is>
-          <t>3II/5, 11/13</t>
+          <t>3II/5, 11/15</t>
         </is>
       </c>
       <c r="U7" s="12" t="inlineStr">
@@ -9615,7 +9623,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 15</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr"/>
@@ -9634,7 +9642,7 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 3II/5, 11/13</t>
+          <t>B1, 1I, 3II/5, 11/15</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
@@ -9689,7 +9697,7 @@
       <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 13</t>
+          <t>3I, 7, 15</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -9709,7 +9717,7 @@
       <c r="Q9" s="12" t="inlineStr"/>
       <c r="R9" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 1II, A1, 3I, 7, 11/13</t>
+          <t>B1, 1I, 1II, A1, 3I, 7, 11/15</t>
         </is>
       </c>
       <c r="S9" s="12" t="inlineStr"/>
@@ -9773,7 +9781,7 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 15</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr"/>
@@ -9843,7 +9851,7 @@
       <c r="I11" s="10" t="inlineStr"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 13</t>
+          <t>3I, 7, 15</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -9923,7 +9931,7 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr"/>
@@ -9942,7 +9950,7 @@
       <c r="Q12" s="12" t="inlineStr"/>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 3II/5, 11/13</t>
+          <t>B1, 1I, 3II/5, 11/15</t>
         </is>
       </c>
       <c r="S12" s="12" t="inlineStr"/>
@@ -9997,7 +10005,7 @@
       <c r="I13" s="10" t="inlineStr"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 11, 13</t>
+          <t>3I, 7, 11, 15</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -10017,7 +10025,7 @@
       <c r="Q13" s="12" t="inlineStr"/>
       <c r="R13" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 1II, A1, 3I, 7, 11/13</t>
+          <t>B1, 1I, 1II, A1, 3I, 7, 11/15</t>
         </is>
       </c>
       <c r="S13" s="12" t="inlineStr"/>
@@ -10081,7 +10089,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr"/>
@@ -10151,7 +10159,7 @@
       <c r="I15" s="10" t="inlineStr"/>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 11, 13</t>
+          <t>3I, 7, 11, 15</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -10238,7 +10246,7 @@
       <c r="M16" s="12" t="inlineStr"/>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>1II, 13, 3I</t>
+          <t>1II, 15, 3I</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr"/>
@@ -10246,7 +10254,7 @@
       <c r="Q16" s="12" t="inlineStr"/>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 3II/5, 9</t>
+          <t>B1, 1I, 3II/5, 9</t>
         </is>
       </c>
       <c r="S16" s="12" t="inlineStr"/>
@@ -10317,13 +10325,13 @@
       <c r="Q17" s="12" t="inlineStr"/>
       <c r="R17" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 1II, A1, 3I, 3II/5, 9</t>
+          <t>B1, 1I, 1II, A1, 3I, 3II/5, 9</t>
         </is>
       </c>
       <c r="S17" s="12" t="inlineStr"/>
       <c r="T17" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U17" s="12" t="inlineStr"/>
@@ -10384,7 +10392,7 @@
       <c r="M18" s="12" t="inlineStr"/>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>1II, 13, 3I</t>
+          <t>1II, 15, 3I</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr"/>
@@ -10461,7 +10469,7 @@
       <c r="S19" s="12" t="inlineStr"/>
       <c r="T19" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U19" s="12" t="inlineStr"/>
@@ -10522,7 +10530,7 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>1II, 13, 3I</t>
+          <t>1II, 15, 3I</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -10530,7 +10538,7 @@
       <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 3II/5, 9</t>
+          <t>B1, 1I, 3II/5, 9</t>
         </is>
       </c>
       <c r="S20" s="12" t="inlineStr"/>
@@ -10597,13 +10605,13 @@
       <c r="Q21" s="12" t="inlineStr"/>
       <c r="R21" s="11" t="inlineStr">
         <is>
-          <t>D1, 1I, 1II, A1, 3I, 3II/5, 9</t>
+          <t>B1, 1I, 1II, A1, 3I, 3II/5, 9</t>
         </is>
       </c>
       <c r="S21" s="12" t="inlineStr"/>
       <c r="T21" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U21" s="12" t="inlineStr"/>
@@ -10664,7 +10672,7 @@
       <c r="M22" s="12" t="inlineStr"/>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>1II, 13, 3I</t>
+          <t>1II, 15, 3I</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr"/>
@@ -10737,7 +10745,7 @@
       <c r="S23" s="12" t="inlineStr"/>
       <c r="T23" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U23" s="12" t="inlineStr"/>
@@ -13175,310 +13183,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -13490,7 +13498,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -13522,7 +13530,7 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I, 1II</t>
+          <t>15, 7, 3I, 1II</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
@@ -13546,7 +13554,7 @@
       <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>11/13, 7, 3I, A1, 1II</t>
+          <t>11/15, 7, 3I, A1, 1II</t>
         </is>
       </c>
       <c r="S6" s="12" t="inlineStr"/>
@@ -13569,7 +13577,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -13601,7 +13609,7 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I, 1II</t>
+          <t>15, 7, 3I, 1II</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -13676,7 +13684,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I, 1II</t>
+          <t>11, 15, 7, 3I, 1II</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr"/>
@@ -13696,7 +13704,7 @@
       <c r="Q8" s="12" t="inlineStr"/>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>11/13, 7, 3I, A1, 1II</t>
+          <t>11/15, 7, 3I, A1, 1II</t>
         </is>
       </c>
       <c r="S8" s="12" t="inlineStr"/>
@@ -13751,7 +13759,7 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I, 1II</t>
+          <t>11, 15, 7, 3I, 1II</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr"/>
@@ -13834,7 +13842,7 @@
       <c r="M10" s="12" t="inlineStr"/>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>13, 1I</t>
+          <t>15, 1I</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr"/>
@@ -13853,7 +13861,7 @@
       </c>
       <c r="U10" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V10" s="11" t="inlineStr"/>
@@ -13917,7 +13925,7 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>13, 1I</t>
+          <t>15, 1I</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
@@ -13932,7 +13940,7 @@
       </c>
       <c r="U11" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
@@ -13996,7 +14004,7 @@
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>13, 1I</t>
+          <t>15, 1I</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr"/>
@@ -14015,7 +14023,7 @@
       </c>
       <c r="U12" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr"/>
@@ -14079,7 +14087,7 @@
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>13, 1I</t>
+          <t>15, 1I</t>
         </is>
       </c>
       <c r="O13" s="12" t="inlineStr"/>
@@ -14094,7 +14102,7 @@
       </c>
       <c r="U13" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
@@ -16825,310 +16833,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -17145,7 +17153,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -17207,7 +17215,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -17239,7 +17247,7 @@
       <c r="I7" s="10" t="inlineStr"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I</t>
+          <t>15, 7, 3I</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -17286,7 +17294,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -17318,7 +17326,7 @@
       <c r="I8" s="10" t="inlineStr"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>13, 7, 3I</t>
+          <t>15, 7, 3I</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
@@ -17393,7 +17401,7 @@
       <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I</t>
+          <t>11, 15, 7, 3I</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr"/>
@@ -17468,7 +17476,7 @@
       <c r="I10" s="10" t="inlineStr"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>11, 13, 7, 3I</t>
+          <t>11, 15, 7, 3I</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr"/>
@@ -17555,7 +17563,7 @@
       <c r="M11" s="12" t="inlineStr"/>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O11" s="12" t="inlineStr"/>
@@ -17574,7 +17582,7 @@
       </c>
       <c r="U11" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V11" s="11" t="inlineStr"/>
@@ -17638,7 +17646,7 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr"/>
@@ -17653,7 +17661,7 @@
       </c>
       <c r="U12" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V12" s="11" t="inlineStr"/>
@@ -17713,7 +17721,7 @@
       <c r="M13" s="12" t="inlineStr"/>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O13" s="12" t="inlineStr"/>
@@ -17732,7 +17740,7 @@
       </c>
       <c r="U13" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V13" s="11" t="inlineStr"/>
@@ -17792,7 +17800,7 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
@@ -17807,7 +17815,7 @@
       </c>
       <c r="U14" s="12" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="V14" s="11" t="inlineStr"/>
@@ -17876,7 +17884,7 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr">
@@ -17955,7 +17963,7 @@
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P16" s="11" t="inlineStr"/>
@@ -17977,7 +17985,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>S2/M2</t>
+          <t>S20/M20</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -17992,7 +18000,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -18010,7 +18018,7 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 15</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr"/>
@@ -18063,7 +18071,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -18081,7 +18089,7 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr"/>
@@ -18134,7 +18142,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -18159,7 +18167,7 @@
       <c r="M19" s="12" t="inlineStr"/>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>13, 3I, 1II</t>
+          <t>15, 3I, 1II</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr"/>
@@ -18197,7 +18205,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -18222,7 +18230,7 @@
       <c r="M20" s="12" t="inlineStr"/>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>13, 3I, 1II</t>
+          <t>15, 3I, 1II</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr"/>
@@ -18260,7 +18268,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -20783,310 +20791,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="53" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B1" s="63" t="n"/>
-      <c r="C1" s="63" t="n"/>
-      <c r="D1" s="63" t="n"/>
-      <c r="E1" s="63" t="n"/>
-      <c r="F1" s="63" t="n"/>
-      <c r="G1" s="63" t="n"/>
-      <c r="H1" s="63" t="n"/>
-      <c r="I1" s="64" t="n"/>
-      <c r="J1" s="55" t="inlineStr">
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="67" t="n"/>
+      <c r="F1" s="67" t="n"/>
+      <c r="G1" s="67" t="n"/>
+      <c r="H1" s="67" t="n"/>
+      <c r="I1" s="68" t="n"/>
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Interlocking</t>
         </is>
       </c>
-      <c r="K1" s="65" t="n"/>
-      <c r="L1" s="65" t="n"/>
-      <c r="M1" s="65" t="n"/>
-      <c r="N1" s="65" t="n"/>
-      <c r="O1" s="65" t="n"/>
-      <c r="P1" s="65" t="n"/>
-      <c r="Q1" s="65" t="n"/>
-      <c r="R1" s="65" t="n"/>
-      <c r="S1" s="65" t="n"/>
-      <c r="T1" s="65" t="n"/>
-      <c r="U1" s="65" t="n"/>
-      <c r="V1" s="65" t="n"/>
-      <c r="W1" s="65" t="n"/>
-      <c r="X1" s="65" t="n"/>
-      <c r="Y1" s="65" t="n"/>
-      <c r="Z1" s="65" t="n"/>
-      <c r="AA1" s="66" t="n"/>
+      <c r="K1" s="69" t="n"/>
+      <c r="L1" s="69" t="n"/>
+      <c r="M1" s="69" t="n"/>
+      <c r="N1" s="69" t="n"/>
+      <c r="O1" s="69" t="n"/>
+      <c r="P1" s="69" t="n"/>
+      <c r="Q1" s="69" t="n"/>
+      <c r="R1" s="69" t="n"/>
+      <c r="S1" s="69" t="n"/>
+      <c r="T1" s="69" t="n"/>
+      <c r="U1" s="69" t="n"/>
+      <c r="V1" s="69" t="n"/>
+      <c r="W1" s="69" t="n"/>
+      <c r="X1" s="69" t="n"/>
+      <c r="Y1" s="69" t="n"/>
+      <c r="Z1" s="69" t="n"/>
+      <c r="AA1" s="70" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="n"/>
-      <c r="I2" s="68" t="n"/>
-      <c r="J2" s="50" t="inlineStr">
+      <c r="A2" s="71" t="n"/>
+      <c r="I2" s="72" t="n"/>
+      <c r="J2" s="49" t="inlineStr">
         <is>
           <t>Required Switches</t>
         </is>
       </c>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="69" t="n"/>
-      <c r="N2" s="69" t="n"/>
-      <c r="O2" s="69" t="n"/>
-      <c r="P2" s="69" t="n"/>
-      <c r="Q2" s="70" t="n"/>
-      <c r="R2" s="50" t="inlineStr">
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="73" t="n"/>
+      <c r="O2" s="73" t="n"/>
+      <c r="P2" s="73" t="n"/>
+      <c r="Q2" s="74" t="n"/>
+      <c r="R2" s="49" t="inlineStr">
         <is>
           <t>Required Sections</t>
         </is>
       </c>
-      <c r="S2" s="69" t="n"/>
-      <c r="T2" s="69" t="n"/>
-      <c r="U2" s="69" t="n"/>
-      <c r="V2" s="69" t="n"/>
-      <c r="W2" s="69" t="n"/>
-      <c r="X2" s="69" t="n"/>
-      <c r="Y2" s="70" t="n"/>
-      <c r="Z2" s="50" t="inlineStr">
+      <c r="S2" s="73" t="n"/>
+      <c r="T2" s="73" t="n"/>
+      <c r="U2" s="73" t="n"/>
+      <c r="V2" s="73" t="n"/>
+      <c r="W2" s="73" t="n"/>
+      <c r="X2" s="73" t="n"/>
+      <c r="Y2" s="74" t="n"/>
+      <c r="Z2" s="49" t="inlineStr">
         <is>
           <t>Required Blocks</t>
         </is>
       </c>
-      <c r="AA2" s="71" t="n"/>
+      <c r="AA2" s="75" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="72" t="n"/>
-      <c r="B3" s="73" t="n"/>
-      <c r="C3" s="73" t="n"/>
-      <c r="D3" s="73" t="n"/>
-      <c r="E3" s="73" t="n"/>
-      <c r="F3" s="73" t="n"/>
-      <c r="G3" s="73" t="n"/>
-      <c r="H3" s="73" t="n"/>
-      <c r="I3" s="74" t="n"/>
-      <c r="J3" s="50" t="inlineStr">
+      <c r="A3" s="76" t="n"/>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+      <c r="I3" s="78" t="n"/>
+      <c r="J3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="K3" s="71" t="n"/>
-      <c r="L3" s="50" t="inlineStr">
+      <c r="K3" s="75" t="n"/>
+      <c r="L3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="M3" s="71" t="n"/>
-      <c r="N3" s="50" t="inlineStr">
+      <c r="M3" s="75" t="n"/>
+      <c r="N3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="O3" s="69" t="n"/>
-      <c r="P3" s="69" t="n"/>
-      <c r="Q3" s="70" t="n"/>
-      <c r="R3" s="50" t="inlineStr">
+      <c r="O3" s="73" t="n"/>
+      <c r="P3" s="73" t="n"/>
+      <c r="Q3" s="74" t="n"/>
+      <c r="R3" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="S3" s="50" t="inlineStr">
+      <c r="S3" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="T3" s="50" t="inlineStr">
+      <c r="T3" s="49" t="inlineStr">
         <is>
           <t>Flank Protection</t>
         </is>
       </c>
-      <c r="U3" s="69" t="n"/>
-      <c r="V3" s="69" t="n"/>
-      <c r="W3" s="69" t="n"/>
-      <c r="X3" s="69" t="n"/>
-      <c r="Y3" s="70" t="n"/>
-      <c r="Z3" s="75" t="n"/>
-      <c r="AA3" s="68" t="n"/>
+      <c r="U3" s="73" t="n"/>
+      <c r="V3" s="73" t="n"/>
+      <c r="W3" s="73" t="n"/>
+      <c r="X3" s="73" t="n"/>
+      <c r="Y3" s="74" t="n"/>
+      <c r="Z3" s="79" t="n"/>
+      <c r="AA3" s="72" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="C4" s="74" t="n"/>
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="E4" s="74" t="n"/>
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="52" t="inlineStr">
+      <c r="H4" s="74" t="n"/>
+      <c r="I4" s="51" t="inlineStr">
         <is>
           <t>Obs.</t>
         </is>
       </c>
-      <c r="J4" s="76" t="n"/>
-      <c r="K4" s="74" t="n"/>
-      <c r="L4" s="76" t="n"/>
-      <c r="M4" s="74" t="n"/>
-      <c r="N4" s="50" t="inlineStr">
+      <c r="J4" s="80" t="n"/>
+      <c r="K4" s="78" t="n"/>
+      <c r="L4" s="80" t="n"/>
+      <c r="M4" s="78" t="n"/>
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="O4" s="70" t="n"/>
-      <c r="P4" s="50" t="inlineStr">
+      <c r="O4" s="74" t="n"/>
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="Q4" s="70" t="n"/>
-      <c r="R4" s="77" t="n"/>
-      <c r="S4" s="77" t="n"/>
-      <c r="T4" s="50" t="inlineStr">
+      <c r="Q4" s="74" t="n"/>
+      <c r="R4" s="81" t="n"/>
+      <c r="S4" s="81" t="n"/>
+      <c r="T4" s="49" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="U4" s="69" t="n"/>
-      <c r="V4" s="70" t="n"/>
-      <c r="W4" s="50" t="inlineStr">
+      <c r="U4" s="73" t="n"/>
+      <c r="V4" s="74" t="n"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="X4" s="69" t="n"/>
-      <c r="Y4" s="70" t="n"/>
-      <c r="Z4" s="76" t="n"/>
-      <c r="AA4" s="74" t="n"/>
+      <c r="X4" s="73" t="n"/>
+      <c r="Y4" s="74" t="n"/>
+      <c r="Z4" s="80" t="n"/>
+      <c r="AA4" s="78" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="78" t="n"/>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="A5" s="82" t="n"/>
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F5" s="79" t="n"/>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="F5" s="83" t="n"/>
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="51" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="I5" s="79" t="n"/>
-      <c r="J5" s="50" t="inlineStr">
+      <c r="I5" s="83" t="n"/>
+      <c r="J5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" s="50" t="inlineStr">
+      <c r="K5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="L5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M5" s="50" t="inlineStr">
+      <c r="M5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="N5" s="50" t="inlineStr">
+      <c r="N5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="O5" s="50" t="inlineStr">
+      <c r="O5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="P5" s="50" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="Q5" s="49" t="inlineStr">
         <is>
           <t>Reverse</t>
         </is>
       </c>
-      <c r="R5" s="79" t="n"/>
-      <c r="S5" s="79" t="n"/>
-      <c r="T5" s="50" t="inlineStr">
+      <c r="R5" s="83" t="n"/>
+      <c r="S5" s="83" t="n"/>
+      <c r="T5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="U5" s="50" t="inlineStr">
+      <c r="U5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="V5" s="50" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="W5" s="50" t="inlineStr">
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>Vital</t>
         </is>
       </c>
-      <c r="X5" s="50" t="inlineStr">
+      <c r="X5" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve"> Sub Vital</t>
         </is>
       </c>
-      <c r="Y5" s="50" t="inlineStr">
+      <c r="Y5" s="49" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="Z5" s="50" t="inlineStr">
+      <c r="Z5" s="49" t="inlineStr">
         <is>
           <t>Up</t>
         </is>
       </c>
-      <c r="AA5" s="57" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>Down</t>
         </is>
@@ -21143,7 +21151,7 @@
       </c>
       <c r="O6" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr"/>
@@ -21193,7 +21201,7 @@
       <c r="I7" s="10" t="inlineStr"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 13</t>
+          <t>3I, 7, 15</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -21265,7 +21273,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>11, 13</t>
+          <t>11, 15</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr"/>
@@ -21331,7 +21339,7 @@
       <c r="I9" s="10" t="inlineStr"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>3I, 7, 11, 13</t>
+          <t>3I, 7, 11, 15</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr"/>
@@ -21399,7 +21407,7 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr"/>
@@ -21478,7 +21486,7 @@
       <c r="N11" s="11" t="inlineStr"/>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr"/>
@@ -21487,7 +21495,7 @@
       <c r="S11" s="12" t="inlineStr"/>
       <c r="T11" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U11" s="12" t="inlineStr"/>
@@ -21544,7 +21552,7 @@
       <c r="M12" s="12" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>13, 3I</t>
+          <t>15, 3I</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr"/>
@@ -21604,7 +21612,7 @@
       <c r="N13" s="11" t="inlineStr"/>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr"/>
@@ -21613,7 +21621,7 @@
       <c r="S13" s="12" t="inlineStr"/>
       <c r="T13" s="11" t="inlineStr">
         <is>
-          <t>7, 11/13</t>
+          <t>7, 11/15</t>
         </is>
       </c>
       <c r="U13" s="12" t="inlineStr"/>
@@ -21670,7 +21678,7 @@
       <c r="M14" s="12" t="inlineStr"/>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>13, 3I</t>
+          <t>15, 3I</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr"/>
@@ -21698,7 +21706,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
@@ -24398,24 +24406,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Overlap</t>
         </is>
       </c>
-      <c r="B1" s="66" t="n"/>
-      <c r="C1" s="55" t="inlineStr">
+      <c r="B1" s="70" t="n"/>
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Approach Route Cancel</t>
         </is>
       </c>
-      <c r="D1" s="66" t="n"/>
-      <c r="E1" s="55" t="inlineStr">
+      <c r="D1" s="70" t="n"/>
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Emergency Route Cancel</t>
         </is>
       </c>
-      <c r="F1" s="66" t="n"/>
+      <c r="F1" s="70" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -24423,27 +24431,27 @@
           <t>Track</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>Destination</t>
         </is>
       </c>
-      <c r="F2" s="57" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Delay [s]</t>
         </is>
@@ -24452,7 +24460,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>11/15</t>
         </is>
       </c>
       <c r="B3" s="12" t="n">
@@ -24610,7 +24618,7 @@
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
@@ -25022,7 +25030,7 @@
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t xml:space="preserve">station_name Cascais
+          <t xml:space="preserve">station_name Cascais (NOT REAL DATA - FOR TESTING ONLY)
 </t>
         </is>
       </c>
@@ -25036,7 +25044,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1II 24980 24908 24749
+          <t xml:space="preserve">    1II 64980 64908 64749
 </t>
         </is>
       </c>
@@ -25062,7 +25070,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    D1 24869 24749
+          <t xml:space="preserve">    B1 64869 64749
 </t>
         </is>
       </c>
@@ -25088,7 +25096,7 @@
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1I 24908 25100 24869
+          <t xml:space="preserve">    1I 64908 65100 64869
 </t>
         </is>
       </c>
@@ -25114,7 +25122,7 @@
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    A1 25100 24980
+          <t xml:space="preserve">    A1 65100 64980
 </t>
         </is>
       </c>
@@ -25140,7 +25148,7 @@
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3I 25174 25141 25100
+          <t xml:space="preserve">    3I 65174 65141 65100
 </t>
         </is>
       </c>
@@ -25161,7 +25169,7 @@
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3II/5 25185 25192 25100 25141
+          <t xml:space="preserve">    3II/5 65185 65192 65100 65141
 </t>
         </is>
       </c>
@@ -25182,7 +25190,7 @@
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7 25230 25210 25174
+          <t xml:space="preserve">    7 65230 65210 65174
 </t>
         </is>
       </c>
@@ -25203,7 +25211,7 @@
       </c>
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11/13 25280 25280 25185 25210
+          <t xml:space="preserve">    11/15 65280 65280 65185 65210
 </t>
         </is>
       </c>
@@ -25224,7 +25232,7 @@
       </c>
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9 25258 25258 25192
+          <t xml:space="preserve">    9 65258 65258 65192
 </t>
         </is>
       </c>
@@ -25239,13 +25247,13 @@
     <row r="12">
       <c r="A12" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC D1
+          <t xml:space="preserve">SEC B1
 </t>
         </is>
       </c>
       <c r="B12" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    R1 25410 25230
+          <t xml:space="preserve">    R1 65410 65230
 </t>
         </is>
       </c>
@@ -25266,7 +25274,7 @@
       </c>
       <c r="B13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    I 25423 25280
+          <t xml:space="preserve">    I 65423 65280
 </t>
         </is>
       </c>
@@ -25287,7 +25295,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    II 25423 25280
+          <t xml:space="preserve">    II 65423 65280
 </t>
         </is>
       </c>
@@ -25308,7 +25316,7 @@
       </c>
       <c r="B15" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    III 25423 25258
+          <t xml:space="preserve">    III 65423 65258
 </t>
         </is>
       </c>
@@ -25329,7 +25337,7 @@
       </c>
       <c r="B16" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    IV 25423 25258
+          <t xml:space="preserve">    IV 65423 65258
 </t>
         </is>
       </c>
@@ -25370,7 +25378,7 @@
       </c>
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1I 24889 24960
+          <t xml:space="preserve">    1I 64889 64960
 </t>
         </is>
       </c>
@@ -25390,7 +25398,7 @@
       </c>
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1II 24960 24889
+          <t xml:space="preserve">    1II 64960 64889
 </t>
         </is>
       </c>
@@ -25404,13 +25412,13 @@
     <row r="20">
       <c r="A20" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE C D1
+          <t xml:space="preserve">    NDE C B1
 </t>
         </is>
       </c>
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3I 25120 25168
+          <t xml:space="preserve">    3I 65120 65168
 </t>
         </is>
       </c>
@@ -25430,7 +25438,7 @@
       </c>
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3II 25180 25120
+          <t xml:space="preserve">    3II 65180 65120
 </t>
         </is>
       </c>
@@ -25450,7 +25458,7 @@
       </c>
       <c r="B22" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 25157 25199
+          <t xml:space="preserve">    5 65157 65199
 </t>
         </is>
       </c>
@@ -25470,7 +25478,7 @@
       </c>
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7 25181 25224
+          <t xml:space="preserve">    7 65181 65224
 </t>
         </is>
       </c>
@@ -25490,7 +25498,7 @@
       </c>
       <c r="B24" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9 25194 25252
+          <t xml:space="preserve">    9 65194 65252
 </t>
         </is>
       </c>
@@ -25510,7 +25518,7 @@
       </c>
       <c r="B25" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11 25217 25274
+          <t xml:space="preserve">    11 65217 65274
 </t>
         </is>
       </c>
@@ -25530,7 +25538,7 @@
       </c>
       <c r="B26" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    13 25256 25191
+          <t xml:space="preserve">    15 65256 65191
 </t>
         </is>
       </c>
@@ -25570,7 +25578,7 @@
       </c>
       <c r="B28" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S1 24741 23791 350
+          <t xml:space="preserve">    S1 64741 63791 350
 </t>
         </is>
       </c>
@@ -25590,7 +25598,7 @@
       </c>
       <c r="B29" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SC1 24741 23794 350
+          <t xml:space="preserve">    SC1 64741 63794 350
 </t>
         </is>
       </c>
@@ -25610,7 +25618,7 @@
       </c>
       <c r="B30" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M_SPE2 24774
+          <t xml:space="preserve">    M_SPE2 64774
 </t>
         </is>
       </c>
@@ -25625,7 +25633,7 @@
       </c>
       <c r="B31" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M1 24868
+          <t xml:space="preserve">    M1 64868
 </t>
         </is>
       </c>
@@ -25634,13 +25642,13 @@
     <row r="32">
       <c r="A32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE A 11/13 -
+          <t xml:space="preserve">    NDE A 11/15 -
 </t>
         </is>
       </c>
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M12 24981
+          <t xml:space="preserve">    M12 64981
 </t>
         </is>
       </c>
@@ -25654,7 +25662,7 @@
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M3 25099
+          <t xml:space="preserve">    M3 65099
 </t>
         </is>
       </c>
@@ -25668,7 +25676,7 @@
       </c>
       <c r="B34" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M5 25099
+          <t xml:space="preserve">    M5 65099
 </t>
         </is>
       </c>
@@ -25682,7 +25690,7 @@
       </c>
       <c r="B35" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    M10 25231
+          <t xml:space="preserve">    M10 65231
 </t>
         </is>
       </c>
@@ -25696,7 +25704,7 @@
       </c>
       <c r="B36" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S2/M2 25275
+          <t xml:space="preserve">    S20/M20 65275
 </t>
         </is>
       </c>
@@ -25710,7 +25718,7 @@
       </c>
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S4/M4 25275
+          <t xml:space="preserve">    S4/M4 65275
 </t>
         </is>
       </c>
@@ -25724,7 +25732,7 @@
       </c>
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S6/M6 25263
+          <t xml:space="preserve">    S6/M6 65263
 </t>
         </is>
       </c>
@@ -25738,7 +25746,7 @@
       </c>
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    S8/M8 25263
+          <t xml:space="preserve">    S8/M8 65263
 </t>
         </is>
       </c>
@@ -25773,7 +25781,7 @@
     <row r="43">
       <c r="A43" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B 11/13
+          <t xml:space="preserve">    NDE B 11/15
 </t>
         </is>
       </c>
@@ -25791,7 +25799,7 @@
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC 11/13 TJD
+          <t xml:space="preserve">SEC 11/15 TJD
 </t>
         </is>
       </c>
@@ -25809,7 +25817,7 @@
     <row r="47">
       <c r="A47" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWP S2/M2
+          <t xml:space="preserve">        SWP S20/M20
 </t>
         </is>
       </c>
@@ -25854,7 +25862,7 @@
     <row r="52">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">        SWI 13
+          <t xml:space="preserve">        SWI 15
 </t>
         </is>
       </c>
@@ -25980,7 +25988,7 @@
     <row r="66">
       <c r="A66" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B 11/13
+          <t xml:space="preserve">    NDE B 11/15
 </t>
         </is>
       </c>
@@ -26007,7 +26015,7 @@
     <row r="69">
       <c r="A69" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NDE B 11/13
+          <t xml:space="preserve">    NDE B 11/15
 </t>
         </is>
       </c>
